--- a/artfynd/A 27374-2022 artfynd.xlsx
+++ b/artfynd/A 27374-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 27374-2022 artfynd.xlsx
+++ b/artfynd/A 27374-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>96435329</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551107.7737243111</v>
+        <v>551108</v>
       </c>
       <c r="R2" t="n">
-        <v>6706170.235505253</v>
+        <v>6706170</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -788,15 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96435528</v>
+        <v>96436230</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,36 +794,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Säter, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551145.6453650135</v>
+        <v>551170</v>
       </c>
       <c r="R3" t="n">
-        <v>6706110.634699454</v>
+        <v>6706264</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,7 +854,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,12 +864,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>50-tal bladrosetter</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +891,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96435959</v>
+        <v>96435383</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219862</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551150.440087884</v>
+        <v>551108</v>
       </c>
       <c r="R4" t="n">
-        <v>6706190.555041406</v>
+        <v>6706136</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,14 +973,14 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -1021,51 +1000,47 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96436230</v>
+        <v>96435168</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Säter, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551169.6467898856</v>
+        <v>551103</v>
       </c>
       <c r="R5" t="n">
-        <v>6706263.776850381</v>
+        <v>6706219</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1097,7 +1072,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,7 +1082,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,15 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96435934</v>
+        <v>96435212</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551166.7295135293</v>
+        <v>551084</v>
       </c>
       <c r="R6" t="n">
-        <v>6706190.785400394</v>
+        <v>6706224</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1211,7 +1181,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1191,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,15 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96435681</v>
+        <v>96435369</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551170.7660149503</v>
+        <v>551108</v>
       </c>
       <c r="R7" t="n">
-        <v>6706079.935685356</v>
+        <v>6706170</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,12 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>50-tal bladrosetter</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,15 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96435856</v>
+        <v>96435528</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551137.7871189974</v>
+        <v>551146</v>
       </c>
       <c r="R8" t="n">
-        <v>6706177.560435798</v>
+        <v>6706111</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,7 +1399,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,7 +1409,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>50-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,15 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96435212</v>
+        <v>96435607</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551084.3016220664</v>
+        <v>551057</v>
       </c>
       <c r="R9" t="n">
-        <v>6706224.124123918</v>
+        <v>6706166</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1558,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,27 +1538,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96435168</v>
+        <v>96435681</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551103.1355448525</v>
+        <v>551171</v>
       </c>
       <c r="R10" t="n">
-        <v>6706218.968153299</v>
+        <v>6706080</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1672,7 +1622,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1682,7 +1632,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>50-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,12 +1667,7 @@
         <v>96435729</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1751,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551181.7919004236</v>
+        <v>551182</v>
       </c>
       <c r="R11" t="n">
-        <v>6706103.25913826</v>
+        <v>6706103</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1823,15 +1773,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96435369</v>
+        <v>96435856</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551107.7737243111</v>
+        <v>551138</v>
       </c>
       <c r="R12" t="n">
-        <v>6706170.235505253</v>
+        <v>6706178</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1900,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,6 +1879,224 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>96435934</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Säter, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>551167</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6706191</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-10-03</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-10-03</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>96435959</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Säter, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>551150</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6706191</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-10-03</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-10-03</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27374-2022 artfynd.xlsx
+++ b/artfynd/A 27374-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96435329</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96436230</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96435383</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96435168</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96435212</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96435369</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1438,6 +1473,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96435528</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1547,6 +1587,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96435607</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1661,6 +1706,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96435681</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1770,6 +1820,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96435729</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1879,6 +1934,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96435856</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1988,6 +2048,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96435934</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2097,8 +2162,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96435959</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>